--- a/Stats.xlsx
+++ b/Stats.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomdy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591E8BE8-AC03-457A-B945-B54FBBBCE1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E80CD5-9D15-4475-B9E6-1C8633F0DDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{BDA9C8D2-A2BE-4A14-B1DD-29E54B7FFE95}"/>
+    <workbookView xWindow="17470" yWindow="0" windowWidth="8220" windowHeight="13770" xr2:uid="{BDA9C8D2-A2BE-4A14-B1DD-29E54B7FFE95}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
     <sheet name="List2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">List1!$A$1:$H$772</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">List1!$A$1:$H$788</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3931" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4032" uniqueCount="244">
   <si>
     <t>Arashid</t>
   </si>
@@ -763,6 +763,15 @@
   </si>
   <si>
     <t>Hecarim</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>Leesin</t>
+  </si>
+  <si>
+    <t>Khazix</t>
   </si>
 </sst>
 </file>
@@ -1150,11 +1159,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A135A446-9DC8-43D0-9765-A4459BE68449}">
-  <dimension ref="A1:H788"/>
+  <dimension ref="A1:L808"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.1796875" customWidth="1"/>
     <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.26953125" bestFit="1" customWidth="1"/>
@@ -1191,28 +1200,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
         <v>161</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="1">
-        <v>25</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1</v>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1607,7 +1616,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>231</v>
       </c>
       <c r="B18" t="s">
         <v>156</v>
@@ -1616,45 +1625,45 @@
         <v>161</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18">
-        <v>13</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>6</v>
       </c>
       <c r="H18">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" t="s">
         <v>161</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
         <v>23</v>
       </c>
       <c r="F19">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -1711,28 +1720,28 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
         <v>161</v>
       </c>
       <c r="D22" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
       </c>
-      <c r="F22">
-        <v>12</v>
-      </c>
-      <c r="G22">
-        <v>3</v>
-      </c>
-      <c r="H22">
-        <v>11</v>
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3</v>
+      </c>
+      <c r="H22" s="1">
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -2491,28 +2500,28 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="B52" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
         <v>161</v>
       </c>
       <c r="D52" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="E52" t="s">
-        <v>23</v>
-      </c>
-      <c r="F52">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="F52" s="1">
+        <v>3</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H52" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
@@ -3193,7 +3202,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="B79" t="s">
         <v>156</v>
@@ -3202,45 +3211,45 @@
         <v>161</v>
       </c>
       <c r="D79" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="E79" t="s">
         <v>23</v>
       </c>
       <c r="F79">
-        <v>9</v>
-      </c>
-      <c r="G79">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G79" s="1">
+        <v>2</v>
       </c>
       <c r="H79">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>199</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C80" t="s">
         <v>161</v>
       </c>
       <c r="D80" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E80" t="s">
-        <v>23</v>
-      </c>
-      <c r="F80">
-        <v>9</v>
+        <v>17</v>
+      </c>
+      <c r="F80" s="1">
+        <v>5</v>
       </c>
       <c r="G80" s="1">
         <v>5</v>
       </c>
       <c r="H80">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
@@ -4155,36 +4164,36 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="B116" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C116" t="s">
         <v>161</v>
       </c>
       <c r="D116" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F116">
-        <v>8</v>
-      </c>
-      <c r="G116" s="1">
-        <v>5</v>
+        <v>13</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
       </c>
       <c r="H116">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B117" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C117" t="s">
         <v>161</v>
@@ -4196,65 +4205,65 @@
         <v>23</v>
       </c>
       <c r="F117">
+        <v>3</v>
+      </c>
+      <c r="G117" s="1">
         <v>8</v>
       </c>
-      <c r="G117" s="1">
-        <v>2</v>
-      </c>
       <c r="H117">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B118" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C118" t="s">
         <v>161</v>
       </c>
       <c r="D118" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F118">
-        <v>8</v>
-      </c>
-      <c r="G118" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>2</v>
       </c>
       <c r="H118">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B119" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C119" t="s">
         <v>161</v>
       </c>
       <c r="D119" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="E119" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F119">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G119" s="1">
-        <v>3</v>
-      </c>
-      <c r="H119" s="1">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="H119">
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
@@ -5169,10 +5178,10 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>124</v>
+        <v>14</v>
       </c>
       <c r="B155" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C155" t="s">
         <v>161</v>
@@ -5181,42 +5190,42 @@
         <v>72</v>
       </c>
       <c r="E155" t="s">
-        <v>23</v>
-      </c>
-      <c r="F155">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="F155" s="1">
+        <v>1</v>
       </c>
       <c r="G155" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H155" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="B156" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C156" t="s">
         <v>161</v>
       </c>
       <c r="D156" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="E156" t="s">
         <v>23</v>
       </c>
       <c r="F156">
-        <v>7</v>
-      </c>
-      <c r="G156">
-        <v>5</v>
-      </c>
-      <c r="H156">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="G156" s="1">
+        <v>5</v>
+      </c>
+      <c r="H156" s="1">
+        <v>17</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.35">
@@ -6313,10 +6322,10 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>63</v>
+        <v>220</v>
       </c>
       <c r="B199" t="s">
-        <v>236</v>
+        <v>159</v>
       </c>
       <c r="C199" t="s">
         <v>161</v>
@@ -6327,14 +6336,14 @@
       <c r="E199" t="s">
         <v>23</v>
       </c>
-      <c r="F199">
-        <v>6</v>
+      <c r="F199" s="1">
+        <v>0</v>
       </c>
       <c r="G199" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H199" s="1">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.35">
@@ -7819,7 +7828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>204</v>
       </c>
@@ -7845,7 +7854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>74</v>
       </c>
@@ -7871,148 +7880,151 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>199</v>
+        <v>55</v>
       </c>
       <c r="B259" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C259" t="s">
         <v>161</v>
       </c>
       <c r="D259" t="s">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="E259" t="s">
-        <v>17</v>
-      </c>
-      <c r="F259" s="1">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="F259">
+        <v>0</v>
       </c>
       <c r="G259" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H259">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="B260" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C260" t="s">
         <v>161</v>
       </c>
       <c r="D260" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="E260" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F260" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G260" s="1">
-        <v>3</v>
-      </c>
-      <c r="H260" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+      <c r="H260">
+        <v>10</v>
+      </c>
+      <c r="L260" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B261" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C261" t="s">
         <v>161</v>
       </c>
       <c r="D261" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="E261" t="s">
-        <v>23</v>
-      </c>
-      <c r="F261">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="F261" s="1">
+        <v>1</v>
       </c>
       <c r="G261" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H261">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="B262" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C262" t="s">
         <v>161</v>
       </c>
       <c r="D262" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E262" t="s">
         <v>23</v>
       </c>
       <c r="F262">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G262">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H262">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="B263" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C263" t="s">
         <v>161</v>
       </c>
       <c r="D263" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E263" t="s">
-        <v>17</v>
-      </c>
-      <c r="F263" s="1">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="F263">
+        <v>1</v>
       </c>
       <c r="G263" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H263">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="B264" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C264" t="s">
         <v>161</v>
       </c>
       <c r="D264" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="E264" t="s">
         <v>23</v>
@@ -8020,14 +8032,14 @@
       <c r="F264">
         <v>5</v>
       </c>
-      <c r="G264" s="1">
-        <v>1</v>
+      <c r="G264">
+        <v>5</v>
       </c>
       <c r="H264">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>130</v>
       </c>
@@ -8053,7 +8065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>69</v>
       </c>
@@ -8079,7 +8091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>67</v>
       </c>
@@ -8105,7 +8117,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>232</v>
       </c>
@@ -8131,7 +8143,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>234</v>
       </c>
@@ -8157,7 +8169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>85</v>
       </c>
@@ -8183,7 +8195,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>197</v>
       </c>
@@ -8209,7 +8221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>63</v>
       </c>
@@ -10083,54 +10095,54 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="B344" t="s">
-        <v>236</v>
+        <v>155</v>
       </c>
       <c r="C344" t="s">
         <v>161</v>
       </c>
       <c r="D344" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="E344" t="s">
         <v>17</v>
       </c>
       <c r="F344" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G344" s="1">
-        <v>5</v>
-      </c>
-      <c r="H344" s="1">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="H344">
+        <v>4</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B345" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C345" t="s">
         <v>161</v>
       </c>
       <c r="D345" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="E345" t="s">
         <v>23</v>
       </c>
       <c r="F345">
-        <v>4</v>
-      </c>
-      <c r="G345">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="G345" s="1">
+        <v>2</v>
       </c>
       <c r="H345">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.35">
@@ -12345,158 +12357,158 @@
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="B431" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C431" t="s">
         <v>161</v>
       </c>
       <c r="D431" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E431" t="s">
-        <v>23</v>
-      </c>
-      <c r="F431">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="F431" s="1">
+        <v>2</v>
       </c>
       <c r="G431" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H431">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B432" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C432" t="s">
         <v>161</v>
       </c>
       <c r="D432" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="E432" t="s">
         <v>17</v>
       </c>
       <c r="F432" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G432" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H432">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>234</v>
+        <v>93</v>
       </c>
       <c r="B433" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C433" t="s">
         <v>161</v>
       </c>
       <c r="D433" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="E433" t="s">
-        <v>17</v>
-      </c>
-      <c r="F433" s="1">
-        <v>3</v>
-      </c>
-      <c r="G433" s="1">
-        <v>3</v>
-      </c>
-      <c r="H433" s="1">
-        <v>4</v>
+        <v>23</v>
+      </c>
+      <c r="F433">
+        <v>3</v>
+      </c>
+      <c r="G433">
+        <v>2</v>
+      </c>
+      <c r="H433">
+        <v>10</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="B434" t="s">
-        <v>159</v>
+        <v>235</v>
       </c>
       <c r="C434" t="s">
         <v>161</v>
       </c>
       <c r="D434" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="E434" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F434">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G434" s="1">
-        <v>5</v>
-      </c>
-      <c r="H434">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="H434" s="1">
+        <v>6</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B435" t="s">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="C435" t="s">
         <v>161</v>
       </c>
       <c r="D435" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="E435" t="s">
         <v>23</v>
       </c>
-      <c r="F435">
-        <v>3</v>
-      </c>
-      <c r="G435">
-        <v>2</v>
-      </c>
-      <c r="H435">
-        <v>10</v>
+      <c r="F435" s="1">
+        <v>1</v>
+      </c>
+      <c r="G435" s="1">
+        <v>1</v>
+      </c>
+      <c r="H435" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="B436" t="s">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="C436" t="s">
         <v>161</v>
       </c>
       <c r="D436" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="E436" t="s">
-        <v>23</v>
-      </c>
-      <c r="F436">
-        <v>3</v>
+        <v>17</v>
+      </c>
+      <c r="F436" s="1">
+        <v>0</v>
       </c>
       <c r="G436" s="1">
-        <v>2</v>
-      </c>
-      <c r="H436">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="H436" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.35">
@@ -15023,36 +15035,36 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B534" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="C534" t="s">
         <v>161</v>
       </c>
       <c r="D534" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="E534" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F534" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G534" s="1">
-        <v>2</v>
-      </c>
-      <c r="H534">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H534" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="B535" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C535" t="s">
         <v>161</v>
@@ -15064,39 +15076,39 @@
         <v>23</v>
       </c>
       <c r="F535">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G535" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H535" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B536" t="s">
-        <v>157</v>
+        <v>236</v>
       </c>
       <c r="C536" t="s">
         <v>161</v>
       </c>
       <c r="D536" t="s">
-        <v>182</v>
+        <v>72</v>
       </c>
       <c r="E536" t="s">
         <v>17</v>
       </c>
       <c r="F536" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G536" s="1">
-        <v>4</v>
-      </c>
-      <c r="H536">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="H536" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.35">
@@ -17779,189 +17791,189 @@
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B640" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C640" t="s">
         <v>161</v>
       </c>
       <c r="D640" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="E640" t="s">
-        <v>17</v>
-      </c>
-      <c r="F640" s="1">
-        <v>1</v>
-      </c>
-      <c r="G640" s="1">
-        <v>5</v>
-      </c>
-      <c r="H640" s="1">
-        <v>4</v>
+        <v>23</v>
+      </c>
+      <c r="F640">
+        <v>12</v>
+      </c>
+      <c r="G640">
+        <v>3</v>
+      </c>
+      <c r="H640">
+        <v>11</v>
       </c>
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="B641" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C641" t="s">
         <v>161</v>
       </c>
       <c r="D641" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="E641" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F641">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G641" s="1">
         <v>5</v>
       </c>
-      <c r="H641" s="1">
-        <v>17</v>
+      <c r="H641">
+        <v>3</v>
       </c>
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="B642" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C642" t="s">
         <v>161</v>
       </c>
       <c r="D642" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="E642" t="s">
         <v>23</v>
       </c>
       <c r="F642">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G642" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H642">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="B643" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C643" t="s">
         <v>161</v>
       </c>
       <c r="D643" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E643" t="s">
         <v>17</v>
       </c>
       <c r="F643" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G643" s="1">
         <v>4</v>
       </c>
       <c r="H643">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="B644" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C644" t="s">
         <v>161</v>
       </c>
       <c r="D644" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="E644" t="s">
         <v>17</v>
       </c>
       <c r="F644" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G644" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H644">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="B645" t="s">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="C645" t="s">
         <v>161</v>
       </c>
       <c r="D645" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="E645" t="s">
         <v>23</v>
       </c>
-      <c r="F645" s="1">
-        <v>1</v>
-      </c>
-      <c r="G645" s="1">
-        <v>1</v>
-      </c>
-      <c r="H645" s="1">
-        <v>7</v>
+      <c r="F645">
+        <v>13</v>
+      </c>
+      <c r="G645">
+        <v>0</v>
+      </c>
+      <c r="H645">
+        <v>9</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="B646" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C646" t="s">
         <v>161</v>
       </c>
       <c r="D646" t="s">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="E646" t="s">
-        <v>17</v>
-      </c>
-      <c r="F646" s="1">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="F646">
+        <v>8</v>
       </c>
       <c r="G646" s="1">
-        <v>7</v>
-      </c>
-      <c r="H646" s="1">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H646">
+        <v>11</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B647" t="s">
         <v>158</v>
@@ -17970,19 +17982,19 @@
         <v>161</v>
       </c>
       <c r="D647" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="E647" t="s">
-        <v>17</v>
-      </c>
-      <c r="F647" s="1">
-        <v>1</v>
-      </c>
-      <c r="G647" s="1">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="F647">
+        <v>4</v>
+      </c>
+      <c r="G647">
+        <v>3</v>
       </c>
       <c r="H647">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.35">
@@ -20483,62 +20495,62 @@
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="B744" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C744" t="s">
         <v>161</v>
       </c>
       <c r="D744" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="E744" t="s">
         <v>17</v>
       </c>
-      <c r="F744" s="1">
-        <v>0</v>
+      <c r="F744">
+        <v>8</v>
       </c>
       <c r="G744" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H744">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B745" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C745" t="s">
         <v>161</v>
       </c>
       <c r="D745" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="E745" t="s">
         <v>23</v>
       </c>
       <c r="F745">
-        <v>0</v>
-      </c>
-      <c r="G745">
-        <v>2</v>
-      </c>
-      <c r="H745">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="G745" s="1">
+        <v>3</v>
+      </c>
+      <c r="H745" s="1">
+        <v>6</v>
       </c>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="B746" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C746" t="s">
         <v>161</v>
@@ -20547,50 +20559,50 @@
         <v>72</v>
       </c>
       <c r="E746" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F746" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G746" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H746" s="1">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B747" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C747" t="s">
         <v>161</v>
       </c>
       <c r="D747" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="E747" t="s">
         <v>23</v>
       </c>
-      <c r="F747">
+      <c r="F747" s="1">
         <v>0</v>
       </c>
-      <c r="G747">
-        <v>1</v>
-      </c>
-      <c r="H747">
-        <v>23</v>
+      <c r="G747" s="1">
+        <v>0</v>
+      </c>
+      <c r="H747" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="B748" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C748" t="s">
         <v>161</v>
@@ -20602,96 +20614,96 @@
         <v>23</v>
       </c>
       <c r="F748">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G748" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H748">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="B749" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C749" t="s">
         <v>161</v>
       </c>
       <c r="D749" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E749" t="s">
         <v>17</v>
       </c>
       <c r="F749" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G749" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H749">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="B750" t="s">
-        <v>235</v>
+        <v>158</v>
       </c>
       <c r="C750" t="s">
         <v>161</v>
       </c>
       <c r="D750" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="E750" t="s">
         <v>17</v>
       </c>
       <c r="F750" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G750" s="1">
-        <v>3</v>
-      </c>
-      <c r="H750" s="1">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="H750">
+        <v>5</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="B751" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C751" t="s">
         <v>161</v>
       </c>
       <c r="D751" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E751" t="s">
-        <v>17</v>
-      </c>
-      <c r="F751" s="1">
-        <v>0</v>
-      </c>
-      <c r="G751" s="1">
+        <v>23</v>
+      </c>
+      <c r="F751">
+        <v>7</v>
+      </c>
+      <c r="G751">
         <v>5</v>
       </c>
       <c r="H751">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="B752" t="s">
         <v>158</v>
@@ -20700,19 +20712,19 @@
         <v>161</v>
       </c>
       <c r="D752" t="s">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="E752" t="s">
         <v>23</v>
       </c>
-      <c r="F752" s="1">
-        <v>0</v>
+      <c r="F752">
+        <v>9</v>
       </c>
       <c r="G752" s="1">
-        <v>0</v>
-      </c>
-      <c r="H752" s="1">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="H752">
+        <v>9</v>
       </c>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.35">
@@ -21651,10 +21663,530 @@
         <v>15</v>
       </c>
     </row>
+    <row r="789" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A789" t="s">
+        <v>32</v>
+      </c>
+      <c r="B789" t="s">
+        <v>235</v>
+      </c>
+      <c r="C789" t="s">
+        <v>161</v>
+      </c>
+      <c r="D789" t="s">
+        <v>16</v>
+      </c>
+      <c r="E789" t="s">
+        <v>23</v>
+      </c>
+      <c r="F789">
+        <v>1</v>
+      </c>
+      <c r="G789">
+        <v>3</v>
+      </c>
+      <c r="H789">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A790" t="s">
+        <v>127</v>
+      </c>
+      <c r="B790" t="s">
+        <v>156</v>
+      </c>
+      <c r="C790" t="s">
+        <v>161</v>
+      </c>
+      <c r="D790" t="s">
+        <v>16</v>
+      </c>
+      <c r="E790" t="s">
+        <v>23</v>
+      </c>
+      <c r="F790">
+        <v>7</v>
+      </c>
+      <c r="G790">
+        <v>4</v>
+      </c>
+      <c r="H790">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A791" t="s">
+        <v>145</v>
+      </c>
+      <c r="B791" t="s">
+        <v>236</v>
+      </c>
+      <c r="C791" t="s">
+        <v>161</v>
+      </c>
+      <c r="D791" t="s">
+        <v>16</v>
+      </c>
+      <c r="E791" t="s">
+        <v>23</v>
+      </c>
+      <c r="F791">
+        <v>10</v>
+      </c>
+      <c r="G791">
+        <v>2</v>
+      </c>
+      <c r="H791">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A792" t="s">
+        <v>146</v>
+      </c>
+      <c r="B792" t="s">
+        <v>158</v>
+      </c>
+      <c r="C792" t="s">
+        <v>161</v>
+      </c>
+      <c r="D792" t="s">
+        <v>16</v>
+      </c>
+      <c r="E792" t="s">
+        <v>23</v>
+      </c>
+      <c r="F792">
+        <v>5</v>
+      </c>
+      <c r="G792">
+        <v>3</v>
+      </c>
+      <c r="H792">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A793" t="s">
+        <v>129</v>
+      </c>
+      <c r="B793" t="s">
+        <v>159</v>
+      </c>
+      <c r="C793" t="s">
+        <v>161</v>
+      </c>
+      <c r="D793" t="s">
+        <v>16</v>
+      </c>
+      <c r="E793" t="s">
+        <v>23</v>
+      </c>
+      <c r="F793">
+        <v>0</v>
+      </c>
+      <c r="G793">
+        <v>4</v>
+      </c>
+      <c r="H793">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A794" t="s">
+        <v>106</v>
+      </c>
+      <c r="B794" t="s">
+        <v>18</v>
+      </c>
+      <c r="C794" t="s">
+        <v>16</v>
+      </c>
+      <c r="D794" t="s">
+        <v>161</v>
+      </c>
+      <c r="E794" t="s">
+        <v>17</v>
+      </c>
+      <c r="F794">
+        <v>0</v>
+      </c>
+      <c r="G794">
+        <v>3</v>
+      </c>
+      <c r="H794">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A795" t="s">
+        <v>176</v>
+      </c>
+      <c r="B795" t="s">
+        <v>19</v>
+      </c>
+      <c r="C795" t="s">
+        <v>16</v>
+      </c>
+      <c r="D795" t="s">
+        <v>161</v>
+      </c>
+      <c r="E795" t="s">
+        <v>17</v>
+      </c>
+      <c r="F795">
+        <v>7</v>
+      </c>
+      <c r="G795">
+        <v>7</v>
+      </c>
+      <c r="H795">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A796" t="s">
+        <v>175</v>
+      </c>
+      <c r="B796" t="s">
+        <v>20</v>
+      </c>
+      <c r="C796" t="s">
+        <v>16</v>
+      </c>
+      <c r="D796" t="s">
+        <v>161</v>
+      </c>
+      <c r="E796" t="s">
+        <v>17</v>
+      </c>
+      <c r="F796">
+        <v>4</v>
+      </c>
+      <c r="G796">
+        <v>4</v>
+      </c>
+      <c r="H796">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A797" t="s">
+        <v>38</v>
+      </c>
+      <c r="B797" t="s">
+        <v>21</v>
+      </c>
+      <c r="C797" t="s">
+        <v>16</v>
+      </c>
+      <c r="D797" t="s">
+        <v>161</v>
+      </c>
+      <c r="E797" t="s">
+        <v>17</v>
+      </c>
+      <c r="F797">
+        <v>2</v>
+      </c>
+      <c r="G797">
+        <v>5</v>
+      </c>
+      <c r="H797">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A798" t="s">
+        <v>46</v>
+      </c>
+      <c r="B798" t="s">
+        <v>22</v>
+      </c>
+      <c r="C798" t="s">
+        <v>16</v>
+      </c>
+      <c r="D798" t="s">
+        <v>161</v>
+      </c>
+      <c r="E798" t="s">
+        <v>17</v>
+      </c>
+      <c r="F798">
+        <v>3</v>
+      </c>
+      <c r="G798">
+        <v>4</v>
+      </c>
+      <c r="H798">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A799" t="s">
+        <v>111</v>
+      </c>
+      <c r="B799" t="s">
+        <v>235</v>
+      </c>
+      <c r="C799" t="s">
+        <v>161</v>
+      </c>
+      <c r="D799" t="s">
+        <v>16</v>
+      </c>
+      <c r="E799" t="s">
+        <v>23</v>
+      </c>
+      <c r="F799">
+        <v>1</v>
+      </c>
+      <c r="G799">
+        <v>2</v>
+      </c>
+      <c r="H799">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A800" t="s">
+        <v>242</v>
+      </c>
+      <c r="B800" t="s">
+        <v>156</v>
+      </c>
+      <c r="C800" t="s">
+        <v>161</v>
+      </c>
+      <c r="D800" t="s">
+        <v>16</v>
+      </c>
+      <c r="E800" t="s">
+        <v>23</v>
+      </c>
+      <c r="F800">
+        <v>6</v>
+      </c>
+      <c r="G800">
+        <v>2</v>
+      </c>
+      <c r="H800">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="801" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A801" t="s">
+        <v>137</v>
+      </c>
+      <c r="B801" t="s">
+        <v>236</v>
+      </c>
+      <c r="C801" t="s">
+        <v>161</v>
+      </c>
+      <c r="D801" t="s">
+        <v>16</v>
+      </c>
+      <c r="E801" t="s">
+        <v>23</v>
+      </c>
+      <c r="F801">
+        <v>13</v>
+      </c>
+      <c r="G801">
+        <v>1</v>
+      </c>
+      <c r="H801">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="802" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A802" t="s">
+        <v>214</v>
+      </c>
+      <c r="B802" t="s">
+        <v>158</v>
+      </c>
+      <c r="C802" t="s">
+        <v>161</v>
+      </c>
+      <c r="D802" t="s">
+        <v>16</v>
+      </c>
+      <c r="E802" t="s">
+        <v>23</v>
+      </c>
+      <c r="F802">
+        <v>4</v>
+      </c>
+      <c r="G802">
+        <v>1</v>
+      </c>
+      <c r="H802">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="803" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A803" t="s">
+        <v>220</v>
+      </c>
+      <c r="B803" t="s">
+        <v>159</v>
+      </c>
+      <c r="C803" t="s">
+        <v>161</v>
+      </c>
+      <c r="D803" t="s">
+        <v>16</v>
+      </c>
+      <c r="E803" t="s">
+        <v>23</v>
+      </c>
+      <c r="F803">
+        <v>0</v>
+      </c>
+      <c r="G803">
+        <v>0</v>
+      </c>
+      <c r="H803">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="804" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A804" t="s">
+        <v>37</v>
+      </c>
+      <c r="B804" t="s">
+        <v>18</v>
+      </c>
+      <c r="C804" t="s">
+        <v>16</v>
+      </c>
+      <c r="D804" t="s">
+        <v>161</v>
+      </c>
+      <c r="E804" t="s">
+        <v>17</v>
+      </c>
+      <c r="F804">
+        <v>4</v>
+      </c>
+      <c r="G804">
+        <v>4</v>
+      </c>
+      <c r="H804">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A805" t="s">
+        <v>243</v>
+      </c>
+      <c r="B805" t="s">
+        <v>19</v>
+      </c>
+      <c r="C805" t="s">
+        <v>16</v>
+      </c>
+      <c r="D805" t="s">
+        <v>161</v>
+      </c>
+      <c r="E805" t="s">
+        <v>17</v>
+      </c>
+      <c r="F805">
+        <v>1</v>
+      </c>
+      <c r="G805">
+        <v>7</v>
+      </c>
+      <c r="H805">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="806" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A806" t="s">
+        <v>107</v>
+      </c>
+      <c r="B806" t="s">
+        <v>20</v>
+      </c>
+      <c r="C806" t="s">
+        <v>16</v>
+      </c>
+      <c r="D806" t="s">
+        <v>161</v>
+      </c>
+      <c r="E806" t="s">
+        <v>17</v>
+      </c>
+      <c r="F806">
+        <v>0</v>
+      </c>
+      <c r="G806">
+        <v>5</v>
+      </c>
+      <c r="H806">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="807" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A807" t="s">
+        <v>34</v>
+      </c>
+      <c r="B807" t="s">
+        <v>21</v>
+      </c>
+      <c r="C807" t="s">
+        <v>16</v>
+      </c>
+      <c r="D807" t="s">
+        <v>161</v>
+      </c>
+      <c r="E807" t="s">
+        <v>17</v>
+      </c>
+      <c r="F807">
+        <v>0</v>
+      </c>
+      <c r="G807">
+        <v>3</v>
+      </c>
+      <c r="H807">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="808" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A808" t="s">
+        <v>39</v>
+      </c>
+      <c r="B808" t="s">
+        <v>22</v>
+      </c>
+      <c r="C808" t="s">
+        <v>16</v>
+      </c>
+      <c r="D808" t="s">
+        <v>161</v>
+      </c>
+      <c r="E808" t="s">
+        <v>17</v>
+      </c>
+      <c r="F808">
+        <v>0</v>
+      </c>
+      <c r="G808">
+        <v>5</v>
+      </c>
+      <c r="H808">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H772" xr:uid="{A135A446-9DC8-43D0-9765-A4459BE68449}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H788">
-      <sortCondition descending="1" ref="F1:F772"/>
+  <autoFilter ref="A1:H788" xr:uid="{A135A446-9DC8-43D0-9765-A4459BE68449}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H752">
+      <sortCondition ref="B1:B788"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -21667,6 +22199,9 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
